--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASDPPractitionerProfile</t>
+    <t>AsDpPractitionerProfile</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:16:04+00:00</t>
+    <t>2023-05-26T10:09:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de as-practitioner dans le contexte de l'Annuaire Santé pour décrire les données d'identification pérennes d’une personne physique, qui travaille en tant que professionnel (professionnel enregistré dans RPPS ou ADELI), personnel autorisé ou personnel d’établissement, dans les domaines sanitaire, médico-social et social.</t>
+    <t>Profil applicatif créé à partir du profil générique as-practitioner dans le contexte des données en libre accès de l’Annuaire Santé.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -445,10 +445,10 @@
     <t>Nationalité du professionnel</t>
   </si>
   <si>
-    <t>Practitioner.extension:as-ext-practitioner-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-practitioner-authorization</t>
+    <t>Practitioner.extension:as-ext-frpractitioner-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization}
@@ -590,7 +590,7 @@
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>Synonymes MOS : typeIdNat_PP,
+    <t>Synonyme : typeIdNat_PP,
 Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
@@ -782,7 +782,8 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idPP</t>
+    <t>Synonyme : idPP
+ Personne/Identifiant PP si l’instance correspond à un identifiant RPPS ou ADELI, sinon Personne/identification nationale PP.</t>
   </si>
   <si>
     <t>123456</t>
@@ -986,7 +987,7 @@
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
   </si>
   <si>
-    <t>Synonyme MOS : civilite</t>
+    <t>Synonyme : civilite</t>
   </si>
   <si>
     <t>Civilités des personnes physiques du RASS</t>
@@ -1078,7 +1079,7 @@
     <t>Les BALs MSS de type PER rattachées seulement à l'identifiant du professionnel de Santé.</t>
   </si>
   <si>
-    <t>Synonyme MOS : boiteLettreMSS</t>
+    <t>Synonyme : boiteLettreMSS</t>
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.id</t>
@@ -1235,7 +1236,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Synonyme MOS : adresseCorrespondance</t>
+    <t>Synonyme : adresseCorrespondance</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
@@ -1250,7 +1251,7 @@
     <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
   </si>
   <si>
-    <t>Synonyme MOS : sexeAdministratif</t>
+    <t>Synonyme : sexeAdministratif</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
@@ -1275,7 +1276,7 @@
     <t>The date of birth for the practitioner.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateNaissance</t>
+    <t>Synonyme : dateNaissance</t>
   </si>
   <si>
     <t>Needed for identification.</t>
@@ -1912,7 +1913,7 @@
     <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
   </si>
   <si>
-    <t>Synonyme MOS : langueParlee</t>
+    <t>Synonyme : langueParlee</t>
   </si>
   <si>
     <t>Knowing which language a practitioner speaks can help in facilitating communication with patients.</t>
@@ -5563,7 +5564,7 @@
         <v>72</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>71</v>
@@ -5665,7 +5666,7 @@
         <v>72</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>71</v>
@@ -5977,7 +5978,7 @@
         <v>72</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>71</v>
@@ -6387,7 +6388,7 @@
         <v>72</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>71</v>
@@ -6797,7 +6798,7 @@
         <v>72</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>71</v>
@@ -6899,7 +6900,7 @@
         <v>72</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>71</v>
@@ -21105,7 +21106,7 @@
         <v>72</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>71</v>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:13:57+00:00</t>
+    <t>2023-06-15T09:14:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Practitioner.meta.extension:as-data-trace</t>
-  </si>
-  <si>
-    <t>as-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t>Practitioner.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:14:52+00:00</t>
+    <t>2023-06-16T14:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1083,7 +1083,7 @@
     <t>Need to know how to reach a practitioner independent to any roles the practitioner may have.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:code}
+    <t xml:space="preserve">profile:$this.resolve()}
 </t>
   </si>
   <si>
@@ -2297,7 +2297,7 @@
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="97.73828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="14.46484375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="21.8671875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="6.9296875" customWidth="true" bestFit="true" hidden="true"/>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-16T14:16:48+00:00</t>
+    <t>2023-07-03T12:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-03T12:37:47+00:00</t>
+    <t>2023-07-10T14:48:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6317" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6316" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:48:30+00:00</t>
+    <t>2023-07-10T14:51:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -870,13 +870,13 @@
     <t>Practitioner.active</t>
   </si>
   <si>
-    <t>Le professionnel est-il actif? active | inactive</t>
+    <t>Le professionnel est-il actif? active | inactive. true  par défaut; false pour les professionnels supprimés</t>
   </si>
   <si>
     <t>Whether this practitioner's record is in active use.</t>
   </si>
   <si>
-    <t>true  par défaut; false pour les professionnels supprimés</t>
+    <t>If the practitioner is not in use by one organization, then it should mark the period on the PractitonerRole with an end date (even if they are active) as they may be active in another role.</t>
   </si>
   <si>
     <t>Need to be able to mark a practitioner record as not to be used because it was created in error.</t>
@@ -892,7 +892,7 @@
 </t>
   </si>
   <si>
-    <t>Une instance pour le nom d’usage et une instance pour le nom issu de l’état-civil</t>
+    <t>Une instance pour le nom d’usage et une instance pour le nom issu de l’état-civil. « usual » pour nom et prénom d’usage (Personne) ; « official » pour nom de famille et prénoms (Etat-civil)</t>
   </si>
   <si>
     <t>A human's name with the ability to identify parts and usage.</t>
@@ -935,7 +935,7 @@
     <t>Identifies the purpose for this name.</t>
   </si>
   <si>
-    <t>« usual » pour nom et prénom d’usage (Personne) ; « official » pour nom de famille et prénoms (Etat-civil)</t>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
@@ -1009,13 +1009,10 @@
     <t>Practitioner.name.prefix</t>
   </si>
   <si>
-    <t>Civilité de la personne physique.</t>
+    <t>Civilité de la personne physique (Synonyme : civilite).</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
-  </si>
-  <si>
-    <t>Synonyme : civilite</t>
   </si>
   <si>
     <t>Civilités des personnes physiques du RASS</t>
@@ -1258,13 +1255,13 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Adresse(s) de correspondance permettant de contacter le professionnel.</t>
+    <t>[Donnée restreinte] : Adresse(s) de correspondance permettant de contacter le professionnel (Synonyme : adresseCorrespondance).</t>
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Synonyme : adresseCorrespondance</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
@@ -1273,13 +1270,10 @@
     <t>Practitioner.gender</t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Sexe administratif de la personne physique, au sens de l'état civil, masculin ou féminin.</t>
+    <t>[Donnée restreinte] : Sexe administratif de la personne physique, au sens de l'état civil, masculin ou féminin (Synonyme : sexeAdministratif).</t>
   </si>
   <si>
     <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
-  </si>
-  <si>
-    <t>Synonyme : sexeAdministratif</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
@@ -1298,13 +1292,10 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Date de naissance de la personne, modifiée selon les règles du RNIV dans le cas des dates exceptionnelles.</t>
+    <t>[Donnée restreinte] : Date de naissance de la personne, modifiée selon les règles du RNIV dans le cas des dates exceptionnelles (Synonyme : dateNaissance).</t>
   </si>
   <si>
     <t>The date of birth for the practitioner.</t>
-  </si>
-  <si>
-    <t>Synonyme : dateNaissance</t>
   </si>
   <si>
     <t>Needed for identification.</t>
@@ -1904,10 +1895,7 @@
     <t>degreeType</t>
   </si>
   <si>
-    <t>Type de diplôme, par exemple : DE, DES, CES, etc.</t>
-  </si>
-  <si>
-    <t>typeDiplome</t>
+    <t>Type de diplôme, par exemple : DE, DES, CES, etc. (typeDiplome)</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
@@ -1947,13 +1935,10 @@
 </t>
   </si>
   <si>
-    <t>Langue parlée.</t>
+    <t>Langue parlée (Synonyme : langueParlee).</t>
   </si>
   <si>
     <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Synonyme : langueParlee</t>
   </si>
   <si>
     <t>Knowing which language a practitioner speaks can help in facilitating communication with patients.</t>
@@ -7562,7 +7547,7 @@
         <v>317</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>318</v>
+        <v>222</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7591,28 +7576,28 @@
         <v>185</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7629,10 +7614,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7658,10 +7643,10 @@
         <v>56</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>222</v>
@@ -7693,28 +7678,28 @@
         <v>105</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Z53" t="s" s="2">
+      <c r="AA53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7731,10 +7716,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7760,16 +7745,16 @@
         <v>257</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
@@ -7818,7 +7803,7 @@
         <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -7835,10 +7820,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7861,19 +7846,19 @@
         <v>43</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
@@ -7910,17 +7895,17 @@
         <v>35</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -7932,18 +7917,18 @@
         <v>54</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>35</v>
@@ -7965,19 +7950,19 @@
         <v>35</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="O56" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>35</v>
@@ -8026,7 +8011,7 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -8038,15 +8023,15 @@
         <v>54</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8143,10 +8128,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8245,13 +8230,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>61</v>
@@ -8273,13 +8258,13 @@
         <v>35</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>65</v>
@@ -8349,10 +8334,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8378,10 +8363,10 @@
         <v>123</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>222</v>
@@ -8398,7 +8383,7 @@
         <v>35</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>35</v>
@@ -8413,37 +8398,37 @@
         <v>185</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AA60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF60" t="s" s="2">
+      <c r="AG60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI60" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>81</v>
@@ -8451,10 +8436,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8480,16 +8465,16 @@
         <v>56</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>35</v>
@@ -8538,7 +8523,7 @@
         <v>35</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -8555,10 +8540,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8584,16 +8569,16 @@
         <v>123</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>35</v>
@@ -8621,28 +8606,28 @@
         <v>185</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8659,10 +8644,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8685,16 +8670,16 @@
         <v>43</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8744,7 +8729,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -8761,10 +8746,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8790,10 +8775,10 @@
         <v>257</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>260</v>
@@ -8846,7 +8831,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -8863,10 +8848,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8889,19 +8874,19 @@
         <v>35</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>35</v>
@@ -8950,7 +8935,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -8967,10 +8952,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8996,16 +8981,16 @@
         <v>123</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>35</v>
@@ -9033,10 +9018,10 @@
         <v>185</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>35</v>
@@ -9054,7 +9039,7 @@
         <v>35</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -9071,10 +9056,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9097,19 +9082,17 @@
         <v>43</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>35</v>
@@ -9158,7 +9141,7 @@
         <v>35</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
@@ -9175,10 +9158,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9201,19 +9184,19 @@
         <v>35</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>35</v>
@@ -9262,7 +9245,7 @@
         <v>35</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
@@ -9274,15 +9257,15 @@
         <v>54</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9305,13 +9288,13 @@
         <v>35</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9362,7 +9345,7 @@
         <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -9379,10 +9362,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9479,10 +9462,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9581,14 +9564,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9610,10 +9593,10 @@
         <v>62</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>65</v>
@@ -9668,7 +9651,7 @@
         <v>35</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
@@ -9685,10 +9668,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9714,14 +9697,14 @@
         <v>174</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>35</v>
@@ -9770,7 +9753,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -9787,10 +9770,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9816,13 +9799,13 @@
         <v>190</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9851,10 +9834,10 @@
         <v>113</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>35</v>
@@ -9872,7 +9855,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>42</v>
@@ -9889,10 +9872,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9989,10 +9972,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10091,10 +10074,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10166,7 +10149,7 @@
         <v>35</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
@@ -10193,13 +10176,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B78" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>35</v>
@@ -10262,7 +10245,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>35</v>
@@ -10297,10 +10280,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10397,10 +10380,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10499,10 +10482,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10528,7 +10511,7 @@
         <v>89</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>209</v>
@@ -10544,7 +10527,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>35</v>
@@ -10603,10 +10586,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10705,10 +10688,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10809,10 +10792,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10913,10 +10896,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11017,13 +11000,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>35</v>
@@ -11086,7 +11069,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>35</v>
@@ -11121,10 +11104,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11221,10 +11204,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11323,10 +11306,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11352,7 +11335,7 @@
         <v>89</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M89" t="s" s="2">
         <v>209</v>
@@ -11368,7 +11351,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>35</v>
@@ -11427,10 +11410,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11529,10 +11512,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11633,10 +11616,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11737,10 +11720,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11841,13 +11824,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>35</v>
@@ -11910,7 +11893,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>35</v>
@@ -11945,10 +11928,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12045,10 +12028,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12147,10 +12130,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12176,7 +12159,7 @@
         <v>89</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M97" t="s" s="2">
         <v>209</v>
@@ -12192,7 +12175,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>35</v>
@@ -12251,10 +12234,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12353,10 +12336,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12457,10 +12440,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12561,10 +12544,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12665,13 +12648,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>35</v>
@@ -12734,7 +12717,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>35</v>
@@ -12769,10 +12752,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12869,10 +12852,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12971,10 +12954,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13000,10 +12983,10 @@
         <v>89</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>210</v>
@@ -13016,7 +12999,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>35</v>
@@ -13075,10 +13058,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13177,10 +13160,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13281,10 +13264,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13385,10 +13368,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13489,13 +13472,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>35</v>
@@ -13558,7 +13541,7 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>35</v>
@@ -13593,10 +13576,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13693,10 +13676,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13795,10 +13778,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13824,7 +13807,7 @@
         <v>89</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>209</v>
@@ -13840,7 +13823,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>35</v>
@@ -13899,10 +13882,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14001,10 +13984,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14105,10 +14088,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14209,10 +14192,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14313,13 +14296,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>35</v>
@@ -14382,7 +14365,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>35</v>
@@ -14417,10 +14400,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14517,10 +14500,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14619,10 +14602,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14648,7 +14631,7 @@
         <v>89</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>209</v>
@@ -14664,7 +14647,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>35</v>
@@ -14723,10 +14706,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14825,10 +14808,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14929,10 +14912,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15033,10 +15016,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15137,13 +15120,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>35</v>
@@ -15206,7 +15189,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>35</v>
@@ -15241,10 +15224,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15341,10 +15324,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15443,10 +15426,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15472,7 +15455,7 @@
         <v>89</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="M129" t="s" s="2">
         <v>209</v>
@@ -15488,7 +15471,7 @@
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>35</v>
@@ -15547,10 +15530,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15649,10 +15632,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15753,10 +15736,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15857,10 +15840,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15961,13 +15944,13 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>35</v>
@@ -16030,7 +16013,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>35</v>
@@ -16065,10 +16048,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16165,10 +16148,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16267,10 +16250,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16296,7 +16279,7 @@
         <v>89</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>209</v>
@@ -16312,7 +16295,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>35</v>
@@ -16371,10 +16354,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16473,10 +16456,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16577,10 +16560,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16681,10 +16664,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16785,13 +16768,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>35</v>
@@ -16854,7 +16837,7 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>35</v>
@@ -16889,10 +16872,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16989,10 +16972,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17091,10 +17074,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17120,10 +17103,10 @@
         <v>89</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="N145" t="s" s="2">
         <v>210</v>
@@ -17136,7 +17119,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>35</v>
@@ -17195,10 +17178,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17297,10 +17280,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17401,10 +17384,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17505,10 +17488,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17609,13 +17592,13 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>35</v>
@@ -17678,7 +17661,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>35</v>
@@ -17713,10 +17696,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17813,10 +17796,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17915,10 +17898,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17944,10 +17927,10 @@
         <v>89</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>210</v>
@@ -17960,7 +17943,7 @@
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>35</v>
@@ -18019,10 +18002,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18121,10 +18104,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18225,10 +18208,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18329,10 +18312,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18433,13 +18416,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>35</v>
@@ -18502,7 +18485,7 @@
       </c>
       <c r="Y158" s="2"/>
       <c r="Z158" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>35</v>
@@ -18537,10 +18520,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18637,10 +18620,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18739,10 +18722,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18768,7 +18751,7 @@
         <v>89</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="M161" t="s" s="2">
         <v>209</v>
@@ -18784,7 +18767,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>35</v>
@@ -18843,10 +18826,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18945,10 +18928,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19049,10 +19032,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19153,10 +19136,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19257,13 +19240,13 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>35</v>
@@ -19326,7 +19309,7 @@
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>35</v>
@@ -19361,10 +19344,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19461,10 +19444,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19563,10 +19546,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19592,10 +19575,10 @@
         <v>89</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>210</v>
@@ -19608,7 +19591,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>35</v>
@@ -19667,10 +19650,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19769,10 +19752,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19873,10 +19856,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19977,10 +19960,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20081,13 +20064,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>35</v>
@@ -20150,7 +20133,7 @@
       </c>
       <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>35</v>
@@ -20185,10 +20168,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20285,10 +20268,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20387,10 +20370,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20416,10 +20399,10 @@
         <v>89</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>210</v>
@@ -20432,7 +20415,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>35</v>
@@ -20491,10 +20474,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20593,10 +20576,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20697,10 +20680,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20801,10 +20784,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20905,13 +20888,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>35</v>
@@ -20974,7 +20957,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>35</v>
@@ -21009,10 +20992,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21109,10 +21092,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21211,10 +21194,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21240,7 +21223,7 @@
         <v>89</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="M185" t="s" s="2">
         <v>209</v>
@@ -21256,7 +21239,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>35</v>
@@ -21315,10 +21298,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21417,10 +21400,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21521,10 +21504,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21625,10 +21608,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21729,13 +21712,13 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D190" t="s" s="2">
         <v>35</v>
@@ -21760,13 +21743,13 @@
         <v>101</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="M190" t="s" s="2">
         <v>201</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>610</v>
+        <v>202</v>
       </c>
       <c r="O190" t="s" s="2">
         <v>203</v>
@@ -21798,7 +21781,7 @@
       </c>
       <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>35</v>
@@ -21833,10 +21816,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21937,10 +21920,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21966,16 +21949,16 @@
         <v>257</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N192" t="s" s="2">
         <v>260</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>35</v>
@@ -22024,7 +22007,7 @@
         <v>35</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>36</v>
@@ -22041,10 +22024,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22070,13 +22053,13 @@
         <v>264</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -22126,7 +22109,7 @@
         <v>35</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>36</v>
@@ -22143,10 +22126,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22169,19 +22152,19 @@
         <v>35</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>625</v>
+        <v>435</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>35</v>
@@ -22210,7 +22193,7 @@
       </c>
       <c r="Y194" s="2"/>
       <c r="Z194" t="s" s="2">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>35</v>
@@ -22228,7 +22211,7 @@
         <v>35</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1490,7 +1490,7 @@
 </t>
   </si>
   <si>
-    <t>Différentes instances pour les téléphones, la télécopie et l’adresse mail.</t>
+    <t>[Donnée restreinte] : telecommunication. Différentes instances pour les téléphones, la télécopie et l’adresse mail.</t>
   </si>
   <si>
     <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,7 +745,8 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1015,8 +1016,7 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+    <t>Description of identifier</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -10980,7 +10980,7 @@
         <v>231</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>233</v>
@@ -13034,7 +13034,7 @@
         <v>231</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>233</v>
@@ -15088,7 +15088,7 @@
         <v>231</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>233</v>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6041,7 +6041,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -15691,7 +15691,7 @@
         <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
@@ -15795,7 +15795,7 @@
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -16101,7 +16101,7 @@
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>73</v>
@@ -16205,7 +16205,7 @@
         <v>74</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>73</v>
@@ -16309,7 +16309,7 @@
         <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>82</v>
@@ -16411,7 +16411,7 @@
         <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>82</v>
@@ -16615,7 +16615,7 @@
         <v>74</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
@@ -16717,7 +16717,7 @@
         <v>74</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>73</v>
@@ -18663,7 +18663,7 @@
         <v>74</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>73</v>
@@ -18869,7 +18869,7 @@
         <v>74</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>73</v>
@@ -19377,7 +19377,7 @@
         <v>74</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>73</v>
@@ -31525,7 +31525,7 @@
         <v>74</v>
       </c>
       <c r="G268" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H268" t="s" s="2">
         <v>73</v>
@@ -31629,7 +31629,7 @@
         <v>74</v>
       </c>
       <c r="G269" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H269" t="s" s="2">
         <v>73</v>
@@ -32241,7 +32241,7 @@
         <v>74</v>
       </c>
       <c r="G275" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H275" t="s" s="2">
         <v>73</v>
@@ -45619,7 +45619,7 @@
         <v>74</v>
       </c>
       <c r="G405" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H405" t="s" s="2">
         <v>73</v>
@@ -58487,7 +58487,7 @@
         <v>74</v>
       </c>
       <c r="G530" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H530" t="s" s="2">
         <v>73</v>
@@ -58997,7 +58997,7 @@
         <v>74</v>
       </c>
       <c r="G535" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H535" t="s" s="2">
         <v>73</v>
@@ -71353,7 +71353,7 @@
         <v>74</v>
       </c>
       <c r="G655" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H655" t="s" s="2">
         <v>73</v>
@@ -71457,7 +71457,7 @@
         <v>74</v>
       </c>
       <c r="G656" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H656" t="s" s="2">
         <v>73</v>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21335" uniqueCount="1205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21335" uniqueCount="1206">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2888,426 +2888,424 @@
     <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession</t>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
+  </si>
+  <si>
+    <t>categorieProfession</t>
+  </si>
+  <si>
+    <t>Catégorie professionnelle indiquant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:profession</t>
   </si>
   <si>
     <t>profession</t>
   </si>
   <si>
-    <t>profession : Profession exercée ou future profession de l'étudiant.
-categorieProfessionnelle : Indique si le professionnel exerce sa profession en tant que :
-M: Militaire
-C: Civil
-F: Fonctionnaire
-E: Etudiant</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:categorieProfession</t>
-  </si>
-  <si>
-    <t>categorieProfession</t>
-  </si>
-  <si>
-    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:profession</t>
-  </si>
-  <si>
     <t>Profession exercée : de santé (professionSante) TRE G15, du social (professionSocial) TRE R94, à usage de titre professionnel (usagerTitre) TRE R95, ou autre profession (autreProfession) TRE R291</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J106-EnsembleProfession-RASS/FHIR/JDV-J106-EnsembleProfession-RASS</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.start</t>
+    <t>Practitioner.qualification:exercicePro.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.period.end</t>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
   </si>
   <si>
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.issuer</t>
+    <t>Practitioner.qualification:exercicePro.issuer</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire</t>
@@ -46129,7 +46127,7 @@
         <v>74</v>
       </c>
       <c r="G410" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H410" t="s" s="2">
         <v>73</v>
@@ -46953,7 +46951,7 @@
         <v>74</v>
       </c>
       <c r="G418" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H418" t="s" s="2">
         <v>73</v>
@@ -47777,7 +47775,7 @@
         <v>74</v>
       </c>
       <c r="G426" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H426" t="s" s="2">
         <v>73</v>
@@ -48601,7 +48599,7 @@
         <v>74</v>
       </c>
       <c r="G434" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H434" t="s" s="2">
         <v>73</v>
@@ -49425,7 +49423,7 @@
         <v>74</v>
       </c>
       <c r="G442" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H442" t="s" s="2">
         <v>73</v>
@@ -50249,7 +50247,7 @@
         <v>74</v>
       </c>
       <c r="G450" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H450" t="s" s="2">
         <v>73</v>
@@ -51073,7 +51071,7 @@
         <v>74</v>
       </c>
       <c r="G458" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H458" t="s" s="2">
         <v>73</v>
@@ -51897,7 +51895,7 @@
         <v>74</v>
       </c>
       <c r="G466" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H466" t="s" s="2">
         <v>73</v>
@@ -52721,7 +52719,7 @@
         <v>74</v>
       </c>
       <c r="G474" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H474" t="s" s="2">
         <v>73</v>
@@ -53545,7 +53543,7 @@
         <v>74</v>
       </c>
       <c r="G482" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H482" t="s" s="2">
         <v>73</v>
@@ -54369,7 +54367,7 @@
         <v>74</v>
       </c>
       <c r="G490" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H490" t="s" s="2">
         <v>73</v>
@@ -55193,7 +55191,7 @@
         <v>74</v>
       </c>
       <c r="G498" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H498" t="s" s="2">
         <v>73</v>
@@ -56017,7 +56015,7 @@
         <v>74</v>
       </c>
       <c r="G506" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H506" t="s" s="2">
         <v>73</v>
@@ -56841,7 +56839,7 @@
         <v>74</v>
       </c>
       <c r="G514" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H514" t="s" s="2">
         <v>73</v>
@@ -57759,7 +57757,7 @@
         <v>597</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>928</v>
+        <v>1055</v>
       </c>
       <c r="D523" t="s" s="2">
         <v>73</v>
@@ -57784,7 +57782,7 @@
         <v>140</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="M523" t="s" s="2">
         <v>243</v>
@@ -57822,7 +57820,7 @@
       </c>
       <c r="Y523" s="2"/>
       <c r="Z523" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AA523" t="s" s="2">
         <v>73</v>
@@ -57857,7 +57855,7 @@
     </row>
     <row r="524" hidden="true">
       <c r="A524" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B524" t="s" s="2">
         <v>761</v>
@@ -57961,7 +57959,7 @@
     </row>
     <row r="525" hidden="true">
       <c r="A525" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B525" t="s" s="2">
         <v>762</v>
@@ -58065,7 +58063,7 @@
     </row>
     <row r="526" hidden="true">
       <c r="A526" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B526" t="s" s="2">
         <v>906</v>
@@ -58165,7 +58163,7 @@
     </row>
     <row r="527" hidden="true">
       <c r="A527" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B527" t="s" s="2">
         <v>908</v>
@@ -58267,7 +58265,7 @@
     </row>
     <row r="528" hidden="true">
       <c r="A528" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B528" t="s" s="2">
         <v>910</v>
@@ -58296,7 +58294,7 @@
         <v>911</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="M528" t="s" s="2">
         <v>913</v>
@@ -58369,7 +58367,7 @@
     </row>
     <row r="529" hidden="true">
       <c r="A529" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B529" t="s" s="2">
         <v>918</v>
@@ -58398,7 +58396,7 @@
         <v>911</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="M529" t="s" s="2">
         <v>920</v>
@@ -58473,7 +58471,7 @@
     </row>
     <row r="530" hidden="true">
       <c r="A530" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B530" t="s" s="2">
         <v>766</v>
@@ -58575,13 +58573,13 @@
     </row>
     <row r="531" hidden="true">
       <c r="A531" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B531" t="s" s="2">
         <v>573</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D531" t="s" s="2">
         <v>73</v>
@@ -58606,7 +58604,7 @@
         <v>574</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="M531" t="s" s="2">
         <v>576</v>
@@ -58677,7 +58675,7 @@
     </row>
     <row r="532" hidden="true">
       <c r="A532" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B532" t="s" s="2">
         <v>578</v>
@@ -58777,7 +58775,7 @@
     </row>
     <row r="533" hidden="true">
       <c r="A533" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B533" t="s" s="2">
         <v>579</v>
@@ -58879,7 +58877,7 @@
     </row>
     <row r="534" hidden="true">
       <c r="A534" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B534" t="s" s="2">
         <v>580</v>
@@ -58983,7 +58981,7 @@
     </row>
     <row r="535" hidden="true">
       <c r="A535" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B535" t="s" s="2">
         <v>585</v>
@@ -59085,7 +59083,7 @@
     </row>
     <row r="536" hidden="true">
       <c r="A536" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B536" t="s" s="2">
         <v>589</v>
@@ -59187,7 +59185,7 @@
     </row>
     <row r="537" hidden="true">
       <c r="A537" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B537" t="s" s="2">
         <v>595</v>
@@ -59287,7 +59285,7 @@
     </row>
     <row r="538" hidden="true">
       <c r="A538" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B538" t="s" s="2">
         <v>596</v>
@@ -59389,7 +59387,7 @@
     </row>
     <row r="539" hidden="true">
       <c r="A539" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B539" t="s" s="2">
         <v>597</v>
@@ -59491,7 +59489,7 @@
     </row>
     <row r="540" hidden="true">
       <c r="A540" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>597</v>
@@ -59507,7 +59505,7 @@
         <v>74</v>
       </c>
       <c r="G540" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H540" t="s" s="2">
         <v>73</v>
@@ -59595,7 +59593,7 @@
     </row>
     <row r="541" hidden="true">
       <c r="A541" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B541" t="s" s="2">
         <v>603</v>
@@ -59695,7 +59693,7 @@
     </row>
     <row r="542" hidden="true">
       <c r="A542" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B542" t="s" s="2">
         <v>605</v>
@@ -59797,7 +59795,7 @@
     </row>
     <row r="543" hidden="true">
       <c r="A543" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B543" t="s" s="2">
         <v>607</v>
@@ -59901,7 +59899,7 @@
     </row>
     <row r="544" hidden="true">
       <c r="A544" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B544" t="s" s="2">
         <v>611</v>
@@ -60003,7 +60001,7 @@
     </row>
     <row r="545" hidden="true">
       <c r="A545" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B545" t="s" s="2">
         <v>613</v>
@@ -60107,7 +60105,7 @@
     </row>
     <row r="546" hidden="true">
       <c r="A546" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B546" t="s" s="2">
         <v>615</v>
@@ -60211,7 +60209,7 @@
     </row>
     <row r="547" hidden="true">
       <c r="A547" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B547" t="s" s="2">
         <v>617</v>
@@ -60315,7 +60313,7 @@
     </row>
     <row r="548" hidden="true">
       <c r="A548" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B548" t="s" s="2">
         <v>597</v>
@@ -60331,7 +60329,7 @@
         <v>74</v>
       </c>
       <c r="G548" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H548" t="s" s="2">
         <v>73</v>
@@ -60419,7 +60417,7 @@
     </row>
     <row r="549" hidden="true">
       <c r="A549" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B549" t="s" s="2">
         <v>603</v>
@@ -60519,7 +60517,7 @@
     </row>
     <row r="550" hidden="true">
       <c r="A550" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B550" t="s" s="2">
         <v>605</v>
@@ -60621,7 +60619,7 @@
     </row>
     <row r="551" hidden="true">
       <c r="A551" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B551" t="s" s="2">
         <v>607</v>
@@ -60725,7 +60723,7 @@
     </row>
     <row r="552" hidden="true">
       <c r="A552" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B552" t="s" s="2">
         <v>611</v>
@@ -60827,7 +60825,7 @@
     </row>
     <row r="553" hidden="true">
       <c r="A553" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B553" t="s" s="2">
         <v>613</v>
@@ -60931,7 +60929,7 @@
     </row>
     <row r="554" hidden="true">
       <c r="A554" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B554" t="s" s="2">
         <v>615</v>
@@ -61035,7 +61033,7 @@
     </row>
     <row r="555" hidden="true">
       <c r="A555" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B555" t="s" s="2">
         <v>617</v>
@@ -61139,7 +61137,7 @@
     </row>
     <row r="556" hidden="true">
       <c r="A556" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B556" t="s" s="2">
         <v>597</v>
@@ -61155,7 +61153,7 @@
         <v>74</v>
       </c>
       <c r="G556" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H556" t="s" s="2">
         <v>73</v>
@@ -61243,7 +61241,7 @@
     </row>
     <row r="557" hidden="true">
       <c r="A557" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B557" t="s" s="2">
         <v>603</v>
@@ -61343,7 +61341,7 @@
     </row>
     <row r="558" hidden="true">
       <c r="A558" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B558" t="s" s="2">
         <v>605</v>
@@ -61445,7 +61443,7 @@
     </row>
     <row r="559" hidden="true">
       <c r="A559" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B559" t="s" s="2">
         <v>607</v>
@@ -61549,7 +61547,7 @@
     </row>
     <row r="560" hidden="true">
       <c r="A560" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B560" t="s" s="2">
         <v>611</v>
@@ -61651,7 +61649,7 @@
     </row>
     <row r="561" hidden="true">
       <c r="A561" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B561" t="s" s="2">
         <v>613</v>
@@ -61755,7 +61753,7 @@
     </row>
     <row r="562" hidden="true">
       <c r="A562" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B562" t="s" s="2">
         <v>615</v>
@@ -61859,7 +61857,7 @@
     </row>
     <row r="563" hidden="true">
       <c r="A563" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B563" t="s" s="2">
         <v>617</v>
@@ -61963,7 +61961,7 @@
     </row>
     <row r="564" hidden="true">
       <c r="A564" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B564" t="s" s="2">
         <v>597</v>
@@ -61979,7 +61977,7 @@
         <v>74</v>
       </c>
       <c r="G564" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H564" t="s" s="2">
         <v>73</v>
@@ -62067,7 +62065,7 @@
     </row>
     <row r="565" hidden="true">
       <c r="A565" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B565" t="s" s="2">
         <v>603</v>
@@ -62167,7 +62165,7 @@
     </row>
     <row r="566" hidden="true">
       <c r="A566" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B566" t="s" s="2">
         <v>605</v>
@@ -62269,7 +62267,7 @@
     </row>
     <row r="567" hidden="true">
       <c r="A567" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B567" t="s" s="2">
         <v>607</v>
@@ -62373,7 +62371,7 @@
     </row>
     <row r="568" hidden="true">
       <c r="A568" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B568" t="s" s="2">
         <v>611</v>
@@ -62475,7 +62473,7 @@
     </row>
     <row r="569" hidden="true">
       <c r="A569" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B569" t="s" s="2">
         <v>613</v>
@@ -62579,7 +62577,7 @@
     </row>
     <row r="570" hidden="true">
       <c r="A570" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B570" t="s" s="2">
         <v>615</v>
@@ -62683,7 +62681,7 @@
     </row>
     <row r="571" hidden="true">
       <c r="A571" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B571" t="s" s="2">
         <v>617</v>
@@ -62787,7 +62785,7 @@
     </row>
     <row r="572" hidden="true">
       <c r="A572" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B572" t="s" s="2">
         <v>597</v>
@@ -62803,7 +62801,7 @@
         <v>74</v>
       </c>
       <c r="G572" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H572" t="s" s="2">
         <v>73</v>
@@ -62891,7 +62889,7 @@
     </row>
     <row r="573" hidden="true">
       <c r="A573" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B573" t="s" s="2">
         <v>603</v>
@@ -62991,7 +62989,7 @@
     </row>
     <row r="574" hidden="true">
       <c r="A574" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B574" t="s" s="2">
         <v>605</v>
@@ -63093,7 +63091,7 @@
     </row>
     <row r="575" hidden="true">
       <c r="A575" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B575" t="s" s="2">
         <v>607</v>
@@ -63197,7 +63195,7 @@
     </row>
     <row r="576" hidden="true">
       <c r="A576" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B576" t="s" s="2">
         <v>611</v>
@@ -63299,7 +63297,7 @@
     </row>
     <row r="577" hidden="true">
       <c r="A577" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B577" t="s" s="2">
         <v>613</v>
@@ -63403,7 +63401,7 @@
     </row>
     <row r="578" hidden="true">
       <c r="A578" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B578" t="s" s="2">
         <v>615</v>
@@ -63507,7 +63505,7 @@
     </row>
     <row r="579" hidden="true">
       <c r="A579" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B579" t="s" s="2">
         <v>617</v>
@@ -63611,7 +63609,7 @@
     </row>
     <row r="580" hidden="true">
       <c r="A580" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B580" t="s" s="2">
         <v>597</v>
@@ -63627,7 +63625,7 @@
         <v>74</v>
       </c>
       <c r="G580" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H580" t="s" s="2">
         <v>73</v>
@@ -63715,7 +63713,7 @@
     </row>
     <row r="581" hidden="true">
       <c r="A581" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B581" t="s" s="2">
         <v>603</v>
@@ -63815,7 +63813,7 @@
     </row>
     <row r="582" hidden="true">
       <c r="A582" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B582" t="s" s="2">
         <v>605</v>
@@ -63917,7 +63915,7 @@
     </row>
     <row r="583" hidden="true">
       <c r="A583" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B583" t="s" s="2">
         <v>607</v>
@@ -64021,7 +64019,7 @@
     </row>
     <row r="584" hidden="true">
       <c r="A584" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B584" t="s" s="2">
         <v>611</v>
@@ -64123,7 +64121,7 @@
     </row>
     <row r="585" hidden="true">
       <c r="A585" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B585" t="s" s="2">
         <v>613</v>
@@ -64227,7 +64225,7 @@
     </row>
     <row r="586" hidden="true">
       <c r="A586" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B586" t="s" s="2">
         <v>615</v>
@@ -64331,7 +64329,7 @@
     </row>
     <row r="587" hidden="true">
       <c r="A587" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B587" t="s" s="2">
         <v>617</v>
@@ -64435,7 +64433,7 @@
     </row>
     <row r="588" hidden="true">
       <c r="A588" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B588" t="s" s="2">
         <v>597</v>
@@ -64451,7 +64449,7 @@
         <v>74</v>
       </c>
       <c r="G588" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H588" t="s" s="2">
         <v>73</v>
@@ -64539,7 +64537,7 @@
     </row>
     <row r="589" hidden="true">
       <c r="A589" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B589" t="s" s="2">
         <v>603</v>
@@ -64639,7 +64637,7 @@
     </row>
     <row r="590" hidden="true">
       <c r="A590" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B590" t="s" s="2">
         <v>605</v>
@@ -64741,7 +64739,7 @@
     </row>
     <row r="591" hidden="true">
       <c r="A591" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B591" t="s" s="2">
         <v>607</v>
@@ -64845,7 +64843,7 @@
     </row>
     <row r="592" hidden="true">
       <c r="A592" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B592" t="s" s="2">
         <v>611</v>
@@ -64947,7 +64945,7 @@
     </row>
     <row r="593" hidden="true">
       <c r="A593" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B593" t="s" s="2">
         <v>613</v>
@@ -65051,7 +65049,7 @@
     </row>
     <row r="594" hidden="true">
       <c r="A594" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B594" t="s" s="2">
         <v>615</v>
@@ -65155,7 +65153,7 @@
     </row>
     <row r="595" hidden="true">
       <c r="A595" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B595" t="s" s="2">
         <v>617</v>
@@ -65259,7 +65257,7 @@
     </row>
     <row r="596" hidden="true">
       <c r="A596" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B596" t="s" s="2">
         <v>597</v>
@@ -65275,7 +65273,7 @@
         <v>74</v>
       </c>
       <c r="G596" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H596" t="s" s="2">
         <v>73</v>
@@ -65363,7 +65361,7 @@
     </row>
     <row r="597" hidden="true">
       <c r="A597" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B597" t="s" s="2">
         <v>603</v>
@@ -65463,7 +65461,7 @@
     </row>
     <row r="598" hidden="true">
       <c r="A598" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B598" t="s" s="2">
         <v>605</v>
@@ -65565,7 +65563,7 @@
     </row>
     <row r="599" hidden="true">
       <c r="A599" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B599" t="s" s="2">
         <v>607</v>
@@ -65669,7 +65667,7 @@
     </row>
     <row r="600" hidden="true">
       <c r="A600" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B600" t="s" s="2">
         <v>611</v>
@@ -65771,7 +65769,7 @@
     </row>
     <row r="601" hidden="true">
       <c r="A601" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B601" t="s" s="2">
         <v>613</v>
@@ -65875,7 +65873,7 @@
     </row>
     <row r="602" hidden="true">
       <c r="A602" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B602" t="s" s="2">
         <v>615</v>
@@ -65979,7 +65977,7 @@
     </row>
     <row r="603" hidden="true">
       <c r="A603" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B603" t="s" s="2">
         <v>617</v>
@@ -66083,7 +66081,7 @@
     </row>
     <row r="604" hidden="true">
       <c r="A604" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B604" t="s" s="2">
         <v>597</v>
@@ -66099,7 +66097,7 @@
         <v>74</v>
       </c>
       <c r="G604" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H604" t="s" s="2">
         <v>73</v>
@@ -66187,7 +66185,7 @@
     </row>
     <row r="605" hidden="true">
       <c r="A605" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B605" t="s" s="2">
         <v>603</v>
@@ -66287,7 +66285,7 @@
     </row>
     <row r="606" hidden="true">
       <c r="A606" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B606" t="s" s="2">
         <v>605</v>
@@ -66389,7 +66387,7 @@
     </row>
     <row r="607" hidden="true">
       <c r="A607" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B607" t="s" s="2">
         <v>607</v>
@@ -66493,7 +66491,7 @@
     </row>
     <row r="608" hidden="true">
       <c r="A608" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B608" t="s" s="2">
         <v>611</v>
@@ -66595,7 +66593,7 @@
     </row>
     <row r="609" hidden="true">
       <c r="A609" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B609" t="s" s="2">
         <v>613</v>
@@ -66699,7 +66697,7 @@
     </row>
     <row r="610" hidden="true">
       <c r="A610" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B610" t="s" s="2">
         <v>615</v>
@@ -66803,7 +66801,7 @@
     </row>
     <row r="611" hidden="true">
       <c r="A611" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B611" t="s" s="2">
         <v>617</v>
@@ -66907,7 +66905,7 @@
     </row>
     <row r="612" hidden="true">
       <c r="A612" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B612" t="s" s="2">
         <v>597</v>
@@ -66923,7 +66921,7 @@
         <v>74</v>
       </c>
       <c r="G612" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H612" t="s" s="2">
         <v>73</v>
@@ -67011,7 +67009,7 @@
     </row>
     <row r="613" hidden="true">
       <c r="A613" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B613" t="s" s="2">
         <v>603</v>
@@ -67111,7 +67109,7 @@
     </row>
     <row r="614" hidden="true">
       <c r="A614" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B614" t="s" s="2">
         <v>605</v>
@@ -67213,7 +67211,7 @@
     </row>
     <row r="615" hidden="true">
       <c r="A615" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B615" t="s" s="2">
         <v>607</v>
@@ -67317,7 +67315,7 @@
     </row>
     <row r="616" hidden="true">
       <c r="A616" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B616" t="s" s="2">
         <v>611</v>
@@ -67419,7 +67417,7 @@
     </row>
     <row r="617" hidden="true">
       <c r="A617" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B617" t="s" s="2">
         <v>613</v>
@@ -67523,7 +67521,7 @@
     </row>
     <row r="618" hidden="true">
       <c r="A618" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B618" t="s" s="2">
         <v>615</v>
@@ -67627,7 +67625,7 @@
     </row>
     <row r="619" hidden="true">
       <c r="A619" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B619" t="s" s="2">
         <v>617</v>
@@ -67731,7 +67729,7 @@
     </row>
     <row r="620" hidden="true">
       <c r="A620" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B620" t="s" s="2">
         <v>597</v>
@@ -67747,7 +67745,7 @@
         <v>74</v>
       </c>
       <c r="G620" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H620" t="s" s="2">
         <v>73</v>
@@ -67835,7 +67833,7 @@
     </row>
     <row r="621" hidden="true">
       <c r="A621" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B621" t="s" s="2">
         <v>603</v>
@@ -67935,7 +67933,7 @@
     </row>
     <row r="622" hidden="true">
       <c r="A622" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B622" t="s" s="2">
         <v>605</v>
@@ -68037,7 +68035,7 @@
     </row>
     <row r="623" hidden="true">
       <c r="A623" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B623" t="s" s="2">
         <v>607</v>
@@ -68141,7 +68139,7 @@
     </row>
     <row r="624" hidden="true">
       <c r="A624" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B624" t="s" s="2">
         <v>611</v>
@@ -68243,7 +68241,7 @@
     </row>
     <row r="625" hidden="true">
       <c r="A625" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B625" t="s" s="2">
         <v>613</v>
@@ -68347,7 +68345,7 @@
     </row>
     <row r="626" hidden="true">
       <c r="A626" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B626" t="s" s="2">
         <v>615</v>
@@ -68451,7 +68449,7 @@
     </row>
     <row r="627" hidden="true">
       <c r="A627" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B627" t="s" s="2">
         <v>617</v>
@@ -68555,7 +68553,7 @@
     </row>
     <row r="628" hidden="true">
       <c r="A628" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B628" t="s" s="2">
         <v>597</v>
@@ -68571,7 +68569,7 @@
         <v>74</v>
       </c>
       <c r="G628" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H628" t="s" s="2">
         <v>73</v>
@@ -68659,7 +68657,7 @@
     </row>
     <row r="629" hidden="true">
       <c r="A629" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B629" t="s" s="2">
         <v>603</v>
@@ -68759,7 +68757,7 @@
     </row>
     <row r="630" hidden="true">
       <c r="A630" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B630" t="s" s="2">
         <v>605</v>
@@ -68861,7 +68859,7 @@
     </row>
     <row r="631" hidden="true">
       <c r="A631" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B631" t="s" s="2">
         <v>607</v>
@@ -68965,7 +68963,7 @@
     </row>
     <row r="632" hidden="true">
       <c r="A632" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B632" t="s" s="2">
         <v>611</v>
@@ -69067,7 +69065,7 @@
     </row>
     <row r="633" hidden="true">
       <c r="A633" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B633" t="s" s="2">
         <v>613</v>
@@ -69171,7 +69169,7 @@
     </row>
     <row r="634" hidden="true">
       <c r="A634" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B634" t="s" s="2">
         <v>615</v>
@@ -69275,7 +69273,7 @@
     </row>
     <row r="635" hidden="true">
       <c r="A635" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B635" t="s" s="2">
         <v>617</v>
@@ -69379,7 +69377,7 @@
     </row>
     <row r="636" hidden="true">
       <c r="A636" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B636" t="s" s="2">
         <v>597</v>
@@ -69395,7 +69393,7 @@
         <v>74</v>
       </c>
       <c r="G636" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H636" t="s" s="2">
         <v>73</v>
@@ -69483,7 +69481,7 @@
     </row>
     <row r="637" hidden="true">
       <c r="A637" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B637" t="s" s="2">
         <v>603</v>
@@ -69583,7 +69581,7 @@
     </row>
     <row r="638" hidden="true">
       <c r="A638" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B638" t="s" s="2">
         <v>605</v>
@@ -69685,7 +69683,7 @@
     </row>
     <row r="639" hidden="true">
       <c r="A639" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B639" t="s" s="2">
         <v>607</v>
@@ -69789,7 +69787,7 @@
     </row>
     <row r="640" hidden="true">
       <c r="A640" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B640" t="s" s="2">
         <v>611</v>
@@ -69891,7 +69889,7 @@
     </row>
     <row r="641" hidden="true">
       <c r="A641" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B641" t="s" s="2">
         <v>613</v>
@@ -69995,7 +69993,7 @@
     </row>
     <row r="642" hidden="true">
       <c r="A642" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B642" t="s" s="2">
         <v>615</v>
@@ -70099,7 +70097,7 @@
     </row>
     <row r="643" hidden="true">
       <c r="A643" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B643" t="s" s="2">
         <v>617</v>
@@ -70203,7 +70201,7 @@
     </row>
     <row r="644" hidden="true">
       <c r="A644" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B644" t="s" s="2">
         <v>597</v>
@@ -70219,7 +70217,7 @@
         <v>74</v>
       </c>
       <c r="G644" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H644" t="s" s="2">
         <v>73</v>
@@ -70307,7 +70305,7 @@
     </row>
     <row r="645" hidden="true">
       <c r="A645" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B645" t="s" s="2">
         <v>603</v>
@@ -70407,7 +70405,7 @@
     </row>
     <row r="646" hidden="true">
       <c r="A646" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B646" t="s" s="2">
         <v>605</v>
@@ -70509,7 +70507,7 @@
     </row>
     <row r="647" hidden="true">
       <c r="A647" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B647" t="s" s="2">
         <v>607</v>
@@ -70613,7 +70611,7 @@
     </row>
     <row r="648" hidden="true">
       <c r="A648" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B648" t="s" s="2">
         <v>611</v>
@@ -70715,7 +70713,7 @@
     </row>
     <row r="649" hidden="true">
       <c r="A649" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B649" t="s" s="2">
         <v>613</v>
@@ -70819,7 +70817,7 @@
     </row>
     <row r="650" hidden="true">
       <c r="A650" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B650" t="s" s="2">
         <v>615</v>
@@ -70923,7 +70921,7 @@
     </row>
     <row r="651" hidden="true">
       <c r="A651" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B651" t="s" s="2">
         <v>617</v>
@@ -71027,13 +71025,13 @@
     </row>
     <row r="652" hidden="true">
       <c r="A652" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B652" t="s" s="2">
         <v>597</v>
       </c>
       <c r="C652" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D652" t="s" s="2">
         <v>73</v>
@@ -71058,7 +71056,7 @@
         <v>140</v>
       </c>
       <c r="L652" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="M652" t="s" s="2">
         <v>243</v>
@@ -71096,7 +71094,7 @@
       </c>
       <c r="Y652" s="2"/>
       <c r="Z652" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="AA652" t="s" s="2">
         <v>73</v>
@@ -71131,13 +71129,13 @@
     </row>
     <row r="653" hidden="true">
       <c r="A653" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B653" t="s" s="2">
         <v>597</v>
       </c>
       <c r="C653" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D653" t="s" s="2">
         <v>73</v>
@@ -71162,7 +71160,7 @@
         <v>140</v>
       </c>
       <c r="L653" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="M653" t="s" s="2">
         <v>243</v>
@@ -71200,7 +71198,7 @@
       </c>
       <c r="Y653" s="2"/>
       <c r="Z653" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="AA653" t="s" s="2">
         <v>73</v>
@@ -71235,7 +71233,7 @@
     </row>
     <row r="654" hidden="true">
       <c r="A654" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B654" t="s" s="2">
         <v>761</v>
@@ -71339,7 +71337,7 @@
     </row>
     <row r="655" hidden="true">
       <c r="A655" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B655" t="s" s="2">
         <v>762</v>
@@ -71443,7 +71441,7 @@
     </row>
     <row r="656" hidden="true">
       <c r="A656" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B656" t="s" s="2">
         <v>766</v>
@@ -71545,10 +71543,10 @@
     </row>
     <row r="657" hidden="true">
       <c r="A657" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B657" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C657" s="2"/>
       <c r="D657" t="s" s="2">
@@ -71571,19 +71569,19 @@
         <v>73</v>
       </c>
       <c r="K657" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="L657" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>592</v>
       </c>
       <c r="O657" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="P657" t="s" s="2">
         <v>73</v>
@@ -71612,7 +71610,7 @@
       </c>
       <c r="Y657" s="2"/>
       <c r="Z657" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="AA657" t="s" s="2">
         <v>73</v>
@@ -71630,7 +71628,7 @@
         <v>73</v>
       </c>
       <c r="AF657" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="AG657" t="s" s="2">
         <v>74</v>
